--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-physical-activity-minutes-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5156" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5156" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1433,6 +1433,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -7742,7 +7746,7 @@
         <v>435</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7751,10 +7755,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7765,10 +7769,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7794,10 +7798,10 @@
         <v>432</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7848,7 +7852,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7860,7 +7864,7 @@
         <v>435</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7869,10 +7873,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7883,10 +7887,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7912,16 +7916,16 @@
         <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7949,10 +7953,10 @@
         <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7970,7 +7974,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7988,10 +7992,10 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>369</v>
@@ -8005,10 +8009,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8034,16 +8038,16 @@
         <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -8071,10 +8075,10 @@
         <v>270</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -8092,7 +8096,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8110,10 +8114,10 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>369</v>
@@ -8127,10 +8131,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8153,17 +8157,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -8212,7 +8216,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8236,7 +8240,7 @@
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -8247,10 +8251,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8276,10 +8280,10 @@
         <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8330,7 +8334,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8351,10 +8355,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -8365,10 +8369,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8391,16 +8395,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8450,7 +8454,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8471,10 +8475,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8485,10 +8489,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8511,16 +8515,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8570,7 +8574,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8591,10 +8595,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8605,10 +8609,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8634,16 +8638,16 @@
         <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8680,7 +8684,7 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8690,7 +8694,7 @@
         <v>169</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8711,10 +8715,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8725,10 +8729,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8843,10 +8847,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8963,10 +8967,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9085,10 +9089,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9114,13 +9118,13 @@
         <v>182</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>268</v>
@@ -9172,7 +9176,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -9190,7 +9194,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>275</v>
@@ -9207,10 +9211,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9236,13 +9240,13 @@
         <v>340</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>344</v>
@@ -9294,7 +9298,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9312,7 +9316,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>347</v>
@@ -9329,10 +9333,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9358,13 +9362,13 @@
         <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>354</v>
@@ -9416,7 +9420,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9451,10 +9455,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9538,7 +9542,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9573,10 +9577,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9602,10 +9606,10 @@
         <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>419</v>
@@ -9660,7 +9664,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9695,13 +9699,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>21</v>
@@ -9726,16 +9730,16 @@
         <v>416</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9784,7 +9788,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9805,10 +9809,10 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9819,10 +9823,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9937,10 +9941,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10057,10 +10061,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10179,10 +10183,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10208,13 +10212,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>268</v>
@@ -10227,7 +10231,7 @@
         <v>21</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>21</v>
@@ -10266,7 +10270,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>93</v>
@@ -10284,7 +10288,7 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>275</v>
@@ -10301,10 +10305,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10327,16 +10331,16 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>344</v>
@@ -10388,7 +10392,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10406,7 +10410,7 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>347</v>
@@ -10423,10 +10427,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10541,10 +10545,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10661,10 +10665,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10687,19 +10691,19 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10748,7 +10752,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10769,10 +10773,10 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>21</v>
@@ -10783,10 +10787,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10812,20 +10816,20 @@
         <v>113</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R70" t="s" s="2">
         <v>21</v>
@@ -10849,10 +10853,10 @@
         <v>176</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10870,7 +10874,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10891,10 +10895,10 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10905,10 +10909,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10934,14 +10938,14 @@
         <v>160</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10951,7 +10955,7 @@
         <v>21</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>21</v>
@@ -10990,7 +10994,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11011,10 +11015,10 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>21</v>
@@ -11025,10 +11029,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11054,14 +11058,14 @@
         <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -11071,7 +11075,7 @@
         <v>21</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>21</v>
@@ -11110,7 +11114,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11119,7 +11123,7 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -11131,10 +11135,10 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
@@ -11145,10 +11149,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11174,16 +11178,16 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11193,7 +11197,7 @@
         <v>21</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>21</v>
@@ -11232,7 +11236,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11253,10 +11257,10 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>21</v>
@@ -11267,10 +11271,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11296,13 +11300,13 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>354</v>
@@ -11354,7 +11358,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11389,10 +11393,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11476,7 +11480,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11511,10 +11515,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11540,10 +11544,10 @@
         <v>83</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>419</v>
@@ -11598,7 +11602,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11633,13 +11637,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
@@ -11664,16 +11668,16 @@
         <v>416</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11722,7 +11726,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11743,10 +11747,10 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
@@ -11757,10 +11761,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11875,10 +11879,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11995,10 +11999,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12117,10 +12121,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12146,13 +12150,13 @@
         <v>182</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>268</v>
@@ -12165,7 +12169,7 @@
         <v>21</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>21</v>
@@ -12204,7 +12208,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -12222,7 +12226,7 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>275</v>
@@ -12239,10 +12243,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12265,16 +12269,16 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>344</v>
@@ -12326,7 +12330,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12344,7 +12348,7 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>347</v>
@@ -12361,10 +12365,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12479,10 +12483,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12599,10 +12603,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12625,19 +12629,19 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12686,7 +12690,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12707,10 +12711,10 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>21</v>
@@ -12721,10 +12725,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12750,20 +12754,20 @@
         <v>113</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q86" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R86" t="s" s="2">
         <v>21</v>
@@ -12787,10 +12791,10 @@
         <v>176</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>21</v>
@@ -12808,7 +12812,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12829,10 +12833,10 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>21</v>
@@ -12843,10 +12847,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12872,14 +12876,14 @@
         <v>160</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -12889,7 +12893,7 @@
         <v>21</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>21</v>
@@ -12928,7 +12932,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12949,10 +12953,10 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>21</v>
@@ -12963,10 +12967,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12992,14 +12996,14 @@
         <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -13009,7 +13013,7 @@
         <v>21</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>21</v>
@@ -13048,7 +13052,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13057,7 +13061,7 @@
         <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>105</v>
@@ -13069,10 +13073,10 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>21</v>
@@ -13083,10 +13087,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13112,16 +13116,16 @@
         <v>113</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -13131,7 +13135,7 @@
         <v>21</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>21</v>
@@ -13170,7 +13174,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13191,10 +13195,10 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>21</v>
@@ -13205,10 +13209,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13234,13 +13238,13 @@
         <v>182</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>354</v>
@@ -13292,7 +13296,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13327,10 +13331,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13414,7 +13418,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13449,10 +13453,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13478,10 +13482,10 @@
         <v>83</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>419</v>
@@ -13536,7 +13540,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13571,13 +13575,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>21</v>
@@ -13602,16 +13606,16 @@
         <v>416</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13660,7 +13664,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13681,10 +13685,10 @@
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13695,10 +13699,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13813,10 +13817,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13933,10 +13937,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14055,10 +14059,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14084,13 +14088,13 @@
         <v>182</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O97" t="s" s="2">
         <v>268</v>
@@ -14142,7 +14146,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>93</v>
@@ -14160,7 +14164,7 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>275</v>
@@ -14177,10 +14181,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14203,16 +14207,16 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O98" t="s" s="2">
         <v>344</v>
@@ -14264,7 +14268,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14282,7 +14286,7 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>347</v>
@@ -14299,10 +14303,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14417,10 +14421,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14537,10 +14541,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14563,19 +14567,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14624,7 +14628,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14645,10 +14649,10 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>21</v>
@@ -14659,10 +14663,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14688,20 +14692,20 @@
         <v>113</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R102" t="s" s="2">
         <v>21</v>
@@ -14725,10 +14729,10 @@
         <v>176</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14746,7 +14750,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14767,10 +14771,10 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>21</v>
@@ -14781,10 +14785,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14810,14 +14814,14 @@
         <v>160</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -14827,7 +14831,7 @@
         <v>21</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>21</v>
@@ -14866,7 +14870,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14887,10 +14891,10 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>21</v>
@@ -14901,10 +14905,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14930,14 +14934,14 @@
         <v>107</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -14947,7 +14951,7 @@
         <v>21</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>21</v>
@@ -14986,7 +14990,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14995,7 +14999,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15007,10 +15011,10 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>21</v>
@@ -15021,10 +15025,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15050,16 +15054,16 @@
         <v>113</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -15069,7 +15073,7 @@
         <v>21</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>21</v>
@@ -15108,7 +15112,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15129,10 +15133,10 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>21</v>
@@ -15143,10 +15147,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15172,13 +15176,13 @@
         <v>182</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>354</v>
@@ -15230,7 +15234,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15265,10 +15269,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15352,7 +15356,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15387,10 +15391,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15416,10 +15420,10 @@
         <v>83</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>419</v>
@@ -15474,7 +15478,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15509,13 +15513,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>21</v>
@@ -15540,16 +15544,16 @@
         <v>416</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -15598,7 +15602,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15619,10 +15623,10 @@
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>21</v>
@@ -15633,10 +15637,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15751,10 +15755,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15871,10 +15875,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15993,10 +15997,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16022,13 +16026,13 @@
         <v>182</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O113" t="s" s="2">
         <v>268</v>
@@ -16041,7 +16045,7 @@
         <v>21</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>21</v>
@@ -16080,7 +16084,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>93</v>
@@ -16098,7 +16102,7 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>275</v>
@@ -16115,10 +16119,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16141,16 +16145,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>344</v>
@@ -16202,7 +16206,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16220,7 +16224,7 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>347</v>
@@ -16237,10 +16241,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16355,10 +16359,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16475,10 +16479,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16501,19 +16505,19 @@
         <v>94</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -16562,7 +16566,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16583,10 +16587,10 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>21</v>
@@ -16597,10 +16601,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16626,20 +16630,20 @@
         <v>113</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q118" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R118" t="s" s="2">
         <v>21</v>
@@ -16663,10 +16667,10 @@
         <v>176</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>21</v>
@@ -16684,7 +16688,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16705,10 +16709,10 @@
         <v>21</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>21</v>
@@ -16719,10 +16723,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16748,14 +16752,14 @@
         <v>160</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16765,7 +16769,7 @@
         <v>21</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>21</v>
@@ -16804,7 +16808,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16825,10 +16829,10 @@
         <v>21</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>21</v>
@@ -16839,10 +16843,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16868,14 +16872,14 @@
         <v>107</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>21</v>
@@ -16885,7 +16889,7 @@
         <v>21</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>21</v>
@@ -16924,7 +16928,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16933,7 +16937,7 @@
         <v>93</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>105</v>
@@ -16945,10 +16949,10 @@
         <v>21</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>21</v>
@@ -16959,10 +16963,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16988,16 +16992,16 @@
         <v>113</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>21</v>
@@ -17007,7 +17011,7 @@
         <v>21</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>21</v>
@@ -17046,7 +17050,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17067,10 +17071,10 @@
         <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>21</v>
@@ -17081,10 +17085,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17110,13 +17114,13 @@
         <v>182</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>354</v>
@@ -17168,7 +17172,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17203,10 +17207,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17290,7 +17294,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17325,10 +17329,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17354,10 +17358,10 @@
         <v>83</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>419</v>
@@ -17412,7 +17416,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17447,13 +17451,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>21</v>
@@ -17478,16 +17482,16 @@
         <v>416</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>21</v>
@@ -17536,7 +17540,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17557,10 +17561,10 @@
         <v>21</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>21</v>
@@ -17571,10 +17575,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17689,10 +17693,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17809,10 +17813,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17931,10 +17935,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17960,13 +17964,13 @@
         <v>182</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O129" t="s" s="2">
         <v>268</v>
@@ -17979,7 +17983,7 @@
         <v>21</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>21</v>
@@ -18018,7 +18022,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>93</v>
@@ -18036,7 +18040,7 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>275</v>
@@ -18053,10 +18057,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18082,13 +18086,13 @@
         <v>182</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O130" t="s" s="2">
         <v>344</v>
@@ -18120,7 +18124,7 @@
       </c>
       <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>21</v>
@@ -18138,7 +18142,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18156,7 +18160,7 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>347</v>
@@ -18173,10 +18177,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18202,13 +18206,13 @@
         <v>182</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O131" t="s" s="2">
         <v>354</v>
@@ -18260,7 +18264,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18295,10 +18299,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18382,7 +18386,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -18417,10 +18421,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18446,10 +18450,10 @@
         <v>83</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>419</v>
@@ -18504,7 +18508,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
